--- a/docs/due-diligence/syntx/models/financial-model.xlsx
+++ b/docs/due-diligence/syntx/models/financial-model.xlsx
@@ -2256,15 +2256,15 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Team cost (S2: 2 разработчика + fractional PM/design)</t>
+          <t>Team cost (S1: 1 AI-first разработчик + fractional legal/design)</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>9000</v>
+        <v>5500</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>USD/мес, см. 08</t>
+          <t>USD/мес — $220/день x 20 дней (см. 08) + ~$1,100 на подрядчиков</t>
         </is>
       </c>
     </row>
